--- a/artfynd/A 34057-2025 artfynd.xlsx
+++ b/artfynd/A 34057-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135657399</v>
+        <v>135691921</v>
       </c>
       <c r="B4" t="n">
-        <v>5181</v>
+        <v>57167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,28 +925,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489368</v>
+        <v>489277</v>
       </c>
       <c r="R4" t="n">
-        <v>6617656</v>
+        <v>6617819</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,14 +990,19 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gnag</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,34 +1011,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135657399</t>
+          <t>https://artportalen.se/Sighting/135691921</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135636942</v>
+        <v>135691957</v>
       </c>
       <c r="B5" t="n">
-        <v>8461</v>
+        <v>57167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,37 +1045,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tixåsarna, Tixåsarna, Vstm</t>
+          <t>Långtjärn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489339</v>
+        <v>489309</v>
       </c>
       <c r="R5" t="n">
-        <v>6617787</v>
+        <v>6617783</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,7 +1122,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,16 +1142,976 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135691957</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135692078</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>489321</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6617733</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135692078</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135692177</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>489333</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6617672</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135692177</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135692405</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>489366</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6617669</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Sandbad m spillning</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135692405</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135692514</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>489372</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6617674</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135692514</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135692614</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>489359</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6617601</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spillning på sten</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135692614</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135692793</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>489359</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6617580</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sandbad i hygget</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135692793</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135657399</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långtjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>489368</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6617656</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gnag</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135657399</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135636942</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tixåsarna, Tixåsarna, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>489339</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6617787</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135636942</t>
         </is>
@@ -1143,6 +2123,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34057-2025 artfynd.xlsx
+++ b/artfynd/A 34057-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135637290</v>
       </c>
       <c r="B2" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135638171</v>
       </c>
       <c r="B3" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135691921</v>
       </c>
       <c r="B4" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>135691957</v>
       </c>
       <c r="B5" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>135692078</v>
       </c>
       <c r="B6" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>135692177</v>
       </c>
       <c r="B7" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>135692405</v>
       </c>
       <c r="B8" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>135692514</v>
       </c>
       <c r="B9" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>135692614</v>
       </c>
       <c r="B10" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>135692793</v>
       </c>
       <c r="B11" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>135657399</v>
       </c>
       <c r="B12" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>135636942</v>
       </c>
       <c r="B13" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
